--- a/Scripts_annehuitema2003/data_output/GP3_improvements_25-24_sessions/income_ratio_satis_plot/Session_240924/vjcortesa_spendshare_meanplayers_S240924_AllRounds_Gall_Pall.xlsx
+++ b/Scripts_annehuitema2003/data_output/GP3_improvements_25-24_sessions/income_ratio_satis_plot/Session_240924/vjcortesa_spendshare_meanplayers_S240924_AllRounds_Gall_Pall.xlsx
@@ -530,13 +530,13 @@
         <v>50.81009588477652</v>
       </c>
       <c r="F6">
-        <v>4.166666666666667</v>
+        <v>4.242424242424242</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6">
-        <v>48.29545454545455</v>
+        <v>49.58677685950413</v>
       </c>
     </row>
     <row r="7">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C65">
-        <v>24000</v>
+        <v>96000</v>
       </c>
       <c r="D65">
-        <v>73000</v>
+        <v>292000</v>
       </c>
       <c r="E65">
-        <v>97000</v>
+        <v>388000</v>
       </c>
       <c r="F65">
         <v>0.2474226804123711</v>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>48.29545454545455</v>
+        <v>49.58677685950413</v>
       </c>
       <c r="D6">
-        <v>4.166666666666667</v>
+        <v>4.242424242424242</v>
       </c>
     </row>
     <row r="7">
